--- a/AAII_Financials/Quarterly/LEVI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEVI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>LEVI</t>
   </si>
@@ -656,519 +656,532 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E7" s="2">
         <v>46082</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45991</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45900</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45809</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45718</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45627</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45529</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45438</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45347</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45256</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45165</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45074</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44983</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44892</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44801</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44710</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44619</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44528</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44437</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44346</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44255</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44164</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44066</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43975</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43884</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43793</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43702</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43611</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43520</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43429</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43338</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43156</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43065</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42974</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42883</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42792</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1562000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1742500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1765800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1543400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1446000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1526800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1749900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1443100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1358800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1480200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1642300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1511000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1336800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1688900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1588700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1517200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1471100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1591600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1684800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1497600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1276000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1305600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1385900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1063100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>497500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1506100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1568600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1447100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1312900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1434500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1591900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1394200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1245700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1343700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1465800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1268400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1067900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1102000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>582900</v>
+      </c>
+      <c r="E9" s="3">
         <v>664200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>693000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>591800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>540200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>579200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>668900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>569200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>526400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>610400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>692600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>671500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>552600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>746600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>701500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>654300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>616100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>648000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>710500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>635400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>525800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>545600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>619300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>485700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>327900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>666800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>717200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>680300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>612500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>651700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>744400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>652600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>574900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>605600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>682600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>611800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>509500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>537400</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>979100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1078300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1072800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>951600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>905800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>947600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1081000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>873900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>832400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>869800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>949700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>839500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>784200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>942300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>887200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>862900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>855000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>943600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>974300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>862200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>750200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>760000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>766600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>577400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>169600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>839300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>851400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>766800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>700400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>782900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>847500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>741600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>670800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>738100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>783200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>656600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>558400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>564600</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1209,8 +1222,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1325,8 +1339,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1441,169 +1458,175 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-13200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11800</v>
       </c>
-      <c r="G14" s="3">
-        <v>11200</v>
-      </c>
       <c r="H14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I14" s="3">
         <v>17600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>24400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>146700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>64200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>132700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>26300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>123500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>27300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>52200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-8400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>35600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>39000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>155400</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>24900</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>22800</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E15" s="3">
         <v>55600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>51800</v>
       </c>
-      <c r="G15" s="3">
-        <v>51500</v>
-      </c>
       <c r="H15" s="3">
+        <v>50300</v>
+      </c>
+      <c r="I15" s="3">
         <v>49200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>43600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>39800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>39600</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1673,8 +1696,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,240 +1738,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1420800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1524700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1550500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1363100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1326800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1322800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1505200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1261000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1273700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1343200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1461400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1371700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1320300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1503600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1451800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1318000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1395000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1344800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1504600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1281300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1199600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1128500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1308600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>970800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>945800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1327300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1437000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1275900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1274900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1233500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1463100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1234700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1168500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1169600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1315900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1122100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1028000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>993700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>141200</v>
+      </c>
+      <c r="E18" s="3">
         <v>217800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>215300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>180300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>119200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>204000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>244700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>182100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>85100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>137000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>180900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>139300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>185300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>136900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>199200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>76100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>246800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>180200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>216300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>76400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>177100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>77300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>92300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-448300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>178800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>131600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>171200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>38000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>201000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>128800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>159500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>77200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>174100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>149900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>146300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>39900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>108300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1986,588 +2019,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-6300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>16200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-9600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-14700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-18100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>206600</v>
+      </c>
+      <c r="E21" s="3">
         <v>283700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>264600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>232300</v>
       </c>
-      <c r="G21" s="3">
-        <v>177000</v>
-      </c>
       <c r="H21" s="3">
+        <v>173400</v>
+      </c>
+      <c r="I21" s="3">
         <v>254300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>286000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>229100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>130600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>174600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>216100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>174400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>52400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>216800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>190000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>234100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>121000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>289100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>216000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>256800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>110100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>213500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>114600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>114000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-411900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>217500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>170200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>198400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>71400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>227800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>173100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>183000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>122100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>197300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>187000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>161400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>50200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>136100</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E22" s="3">
         <v>13100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>25900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>28400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>18300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>15100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>15700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>15500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>16300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>14500</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>17900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E23" s="3">
         <v>228200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>198700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>156200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>176600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>196100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>136600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>139200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>139600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>186300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>77800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>245900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>166800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>203000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>55700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>154700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>52000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>51600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-458200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>164800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>118200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>151600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>181700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>135400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>139900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>75700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>149000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>139000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>117100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>88800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E24" s="3">
         <v>51100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>38500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>34200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>36400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-13000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-10900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>24600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-94600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>12100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>27300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>35300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>34600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>31700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>21700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>27600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-13800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2682,240 +2731,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E26" s="3">
         <v>177100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>160200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>122000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>79600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>140200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>180400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>22700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>126900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>114700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>150600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>173000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>49700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>195800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>153000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>193300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>64700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>142500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>56700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>152700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>95800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>124200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>28500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>146500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>100800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>123200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>77000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>117400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>117200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>89500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>17700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E27" s="3">
         <v>175800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>158000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>218100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>67000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>135000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>182600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>126900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>114700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>150600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>173000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>49700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>195800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>153000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>193300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>64700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>142500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>56700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>152700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>95300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>124500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>28200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>146600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>100600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>123700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>74900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>117000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>115800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>88000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>17500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3030,41 +3088,44 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-2200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>96100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-12600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-5200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>2200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-800</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -3104,8 +3165,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3122,20 +3183,20 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>6400</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-136000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3146,8 +3207,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3262,8 +3326,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3378,240 +3445,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E32" s="3">
         <v>10300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>6300</v>
-      </c>
       <c r="H32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-12900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>9600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>14700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>18100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E33" s="3">
         <v>175800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>158000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>218100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>67000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>135000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>182600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>126900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>114700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>150600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>173000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>49700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>195800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>153000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>193300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>64700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>142500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>56700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>27000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>152700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>95300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>124500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>28200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>146600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>97100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>130100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>74900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>115800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>88000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>17500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3726,245 +3802,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E35" s="3">
         <v>175800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>158000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>218100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>67000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>135000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>182600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>126900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>114700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>150600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>173000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>49700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>195800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>153000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>193300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>64700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>142500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>56700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>27000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>152700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>95300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>124500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>28200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>146600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>97100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>130100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>74900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>115800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>88000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>17500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E38" s="2">
         <v>46082</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45991</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45900</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45809</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45718</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45627</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45529</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45438</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45347</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45256</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45165</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45074</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44983</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44892</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44801</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44710</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44619</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44528</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44437</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44346</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44255</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44164</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44066</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43975</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43884</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43793</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43702</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43611</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43520</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43429</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43338</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43156</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43065</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42974</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42883</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42792</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4005,8 +4090,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4047,142 +4133,146 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>849300</v>
+      </c>
+      <c r="E41" s="3">
         <v>716600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>757900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>612800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>653600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>574400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>690000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>577100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>641400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>516700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>398800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>294500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>471600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>321800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>429600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>498900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>601900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>678300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>810300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1376600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1224100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1973600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1497200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1353000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1448200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>873600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>934200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>863800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>860900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>621900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>713100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>612500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>698700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>590200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>633600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>491300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>437500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>368600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E42" s="3">
         <v>95400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>90900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>94700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4208,55 +4298,55 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>70600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>100500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>96400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>98800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>91600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>95500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>94500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>94300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>96500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>72300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>76100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>84000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>80700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>80200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>79700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>100000</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
@@ -4264,8 +4354,8 @@
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
@@ -4279,472 +4369,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>586200</v>
+      </c>
+      <c r="E43" s="3">
         <v>728900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>774700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>722900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>617500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>654900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>710000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>679500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>581800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>661600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>752700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>690200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>560700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>768700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>697000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>660400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>609200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>648200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>707600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>667300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>579900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>600300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>540200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>543300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>333600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>710000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>782800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>722000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>574400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>633500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>534200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>487200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>342300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>428500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>485500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>446700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>309400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>406700</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1157600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1120600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1237700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1286300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1248900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1073200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1131300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1275200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1220000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1150400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1290100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1373800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1313500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1335200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1416800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1292300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1112800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1006200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>898000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>902300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>863400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>835400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>817700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>944300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>986200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>854700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>884200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>935600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>895300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>914300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>883800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>938300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>842600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>826400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>759400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>826100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>780600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E45" s="3">
         <v>248000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>292500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>290100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>326000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>349000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>319800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>213700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>206800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>196100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>196000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>207200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>198400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>223200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>213900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>227900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>222100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>181500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>202500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>189300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>208200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>192100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>174600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>169000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>208200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>222800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>188200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>212100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>196800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>177500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>157000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>158000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>120700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>137900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>118700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>122800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>114100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2966900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2909500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3153700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3006800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2929100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2651500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2851100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2745500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2650000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2524800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2637600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2565700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2544200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2648900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2827900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2780000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2642400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2613000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2709900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3231000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2970000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3695600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3126200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3081900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3052400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2745000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2870200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2813700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2607100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2447300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2288100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2196000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2004400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1983100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1997200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1886900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1641600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1659200</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4787,8 +4892,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4859,240 +4964,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1801100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1823500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1830000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1807100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1754000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1715500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1752900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1802100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1749100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1695300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1714600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1626000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1638200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1580200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1592800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1541000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1533300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1577600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1606300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1592700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1436100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1447000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1443300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1433400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1421000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1487200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>529600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>498900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>480500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>463800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>460600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>420000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>413200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>415000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>424500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>388700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>390500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>380400</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>474800</v>
+      </c>
+      <c r="E49" s="3">
         <v>476000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>475000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>473500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>473900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>472500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>474200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>479200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>593000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>562300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>571300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>569500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>658000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>655200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>652400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>653000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>657300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>667800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>678200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>312300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>313900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>314300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>312200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>312300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>309000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>310300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>278600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>278400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>278500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>278900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>279100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>279300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>280100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>281600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>280200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>280100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>278900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>277400</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5207,8 +5321,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5323,124 +5440,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>544800</v>
+      </c>
+      <c r="E52" s="3">
         <v>539200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>560000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>560900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>551900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>558200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>498800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>448900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>419600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>417400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>400600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>389500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>382800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>354100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>964700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>925200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>904800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>893300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>905700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>854800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>824600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>779300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>759500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>719700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>705600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>572800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>554100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>548000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>543200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>518300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>514900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>522300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>522400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>538700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>655900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>666300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>644200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>613300</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5555,124 +5678,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6627500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6574800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6848800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6656400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6533200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6198200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6375500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6253500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6185900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5961500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6053600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5874200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5891800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5873900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6037800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5899200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5737800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5751800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5900100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5990800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5544700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6236200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5641200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5547300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5488000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5115200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4232400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4139000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3909400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3708400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3542700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3417700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3220100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3218300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3357800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3222000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2955200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2930300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5713,8 +5842,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5755,704 +5885,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>598500</v>
+      </c>
+      <c r="E57" s="3">
         <v>487600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>597600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>621400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>683500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>556900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>663400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>667800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>623100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>497600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>567900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>573500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>464200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>475400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>657200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>690300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>558700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>563000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>524800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>551500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>436500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>420600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>375500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>461500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>284400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>304200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>360300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>357700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>339500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>329900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>351300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>361700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>328800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>305200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>289500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>300300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>274500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>256700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>266700</v>
+        <v>268300</v>
       </c>
       <c r="E58" s="3">
+        <v>267700</v>
+      </c>
+      <c r="F58" s="3">
         <v>260700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>266800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>260800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>254000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>252900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>261000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>248400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>249900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>258000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>279400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>373800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>396000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>797300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>17600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>307900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>27600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>31900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>35800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>24900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>38500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>33400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>31600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E59" s="3">
         <v>372600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>402300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>383500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>376700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>368400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>378400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>374700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>362900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>369000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>316900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>303600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>295200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>292900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1312700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1166900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1166000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1118800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1338900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1210000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1179500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1105800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1155800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1088700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1000100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>968000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>799300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>800700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>756700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>851000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>668900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>644500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>551800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>579700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>551100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>529500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>427500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>440900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1853200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1845300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2032500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1979000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1979800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1768600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2010500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1946100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1869100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1770400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1787500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1808100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1798400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1774200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1981600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1865600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1730600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1686000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1869600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1769000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1625200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2323700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1548900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1574200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1592400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1291500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1167200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1186000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1107700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1204400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1052200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1042000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>903700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>909800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>879100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>863200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>733600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>731800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2027300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2049900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2044800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2029900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1984300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1903800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1937000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1990400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1943800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1903800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1922500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1827700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1856500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1831800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>984500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>963500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>998500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1020500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1020700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1243300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1263800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1262700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1546700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1499000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>994400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1006700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1007000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1011100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1017700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1020200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1041800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1050400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1078700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1055400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1051200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1022300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1022100</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>230300</v>
+      </c>
+      <c r="E62" s="3">
         <v>231800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>240200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>484800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>44300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>203900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>443900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>419300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>311200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>50300</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="O62" s="3">
-        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
       </c>
       <c r="Q62" s="3">
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
         <v>1168000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1241100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1280300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1321600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1344100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1368500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1221600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1242800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1246200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1238500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1231400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1234500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>486900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>477600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>469300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>477300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>503600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>454600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>483500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>513200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>594000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>592400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>591500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>583300</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6567,8 +6716,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6683,8 +6835,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6799,124 +6954,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4355100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4368200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4570200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4493700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4443200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4163700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4405000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4380400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4232200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3985400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4007200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3932800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3954100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3906400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4134100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4070200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4009400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4028200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4234400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4380900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4110600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4829200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4341800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4356000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4322800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3520400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2668900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2678300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2595900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2706700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2583400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2545800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2445700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2507800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2533900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2510800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2349800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2339400</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6957,8 +7118,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7073,8 +7235,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7189,8 +7354,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7305,8 +7473,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7421,124 +7592,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1896800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1863400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1897300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1806400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1740700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1725600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1672000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1571200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1620000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1666700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1750200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1671000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1709100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1758400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1699400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1628300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1529300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1559300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1474900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1442500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1281400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1240800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1114300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1057400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1030500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1445200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1310500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1219100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1094700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1094600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1084300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1060200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>992400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>949300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1100900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1029300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>942400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>921900</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7653,8 +7830,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7769,8 +7949,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7885,124 +8068,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2272400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2206600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2278600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2162700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2090000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2034500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1970500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1873100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1953700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1976100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2046400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1941400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1937700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1967500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1903700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1829000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1728300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1723600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1665700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1609900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1434000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1407000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1299500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1191300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1165200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1594800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1563500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1460700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1313500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1001600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>959300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>871900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>774400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>710500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>823900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>711100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>605400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>591000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8117,245 +8306,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="E80" s="2">
         <v>46082</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45991</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45900</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45809</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45718</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45627</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45529</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45438</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45347</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45256</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45165</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45074</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44983</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44892</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44801</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44710</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44619</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44528</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44437</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44346</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44255</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44164</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44066</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43975</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43884</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43793</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43702</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43611</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43520</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43429</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43338</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43247</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43156</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43065</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42974</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42883</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42792</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E81" s="3">
         <v>175800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>158000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>218100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>67000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>135000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>182600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>126900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>114700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>150600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>173000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>49700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>195800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>153000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>193300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>64700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>142500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>56700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>27000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-363500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>152700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>95300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>124500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>28200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>146600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>97100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>130100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>74900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>115800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>88000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>17500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>60100</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8396,124 +8594,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>49200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>54100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>43600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>38900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>40200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>38800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>38900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>34500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>35500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>36800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>34000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>35000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>36000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>33600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>30200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>28600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>28100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>27400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>32800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>31800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>29800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>28400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>27400</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8628,8 +8830,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8744,8 +8949,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8860,8 +9068,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8976,8 +9187,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9092,124 +9306,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>211500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>266800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24800</v>
       </c>
-      <c r="G89" s="3">
-        <v>185500</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>52500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>297300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>52300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>262800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>286000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>258900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>286200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-160800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>64400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>59700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>86100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>238400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>250800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>178500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>69500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>228700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>199500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-156500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>197900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>206700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>43700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>106000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>55800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>215600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-22800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>161400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>66200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>231500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>77400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>168000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>49000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9250,124 +9470,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-59400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64200</v>
       </c>
-      <c r="G91" s="3">
-        <v>-39500</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-66600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-50000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-63200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-70500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-110900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-70300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-76300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-73600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-58500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-44400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-51100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-60200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-38100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-25100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9482,8 +9706,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9598,124 +9825,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>26300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-59000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>120000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-58600</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-71100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-88900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-50800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-71700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-79800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-79400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-91900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-57000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-78200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-444100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-57300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-34900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-70800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>11700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-119300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-45000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-63000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-40400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-38000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-41300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-48800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-26800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-32800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-16000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9756,124 +9989,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>53800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>54700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>55400</v>
       </c>
-      <c r="G96" s="3">
-        <v>51400</v>
-      </c>
-      <c r="H96" s="3">
-        <v>51400</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
         <v>51400</v>
       </c>
       <c r="J96" s="3">
+        <v>51400</v>
+      </c>
+      <c r="K96" s="3">
         <v>51500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>47700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>47900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>47600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>47700</v>
-      </c>
-      <c r="O96" s="3">
-        <v>47600</v>
       </c>
       <c r="P96" s="3">
         <v>47600</v>
       </c>
       <c r="Q96" s="3">
+        <v>47600</v>
+      </c>
+      <c r="R96" s="3">
         <v>-47300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-47500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-39700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-39900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-32200</v>
       </c>
       <c r="V96" s="3">
         <v>-32200</v>
       </c>
       <c r="W96" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="X96" s="3">
         <v>-24100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-31700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-31900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-58900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-55000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-45000</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-45000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-35000</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-35000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9988,8 +10225,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10104,8 +10344,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10220,352 +10463,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-284100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-63100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-184700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-54900</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-97500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-90200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-66200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-68400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-94500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-75000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-145000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-71900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>77800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-77700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-70600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-77700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-139400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-351300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-892800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>439700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-287100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>727600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-138000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-91800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>15700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>198800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-67700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-52500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-73900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-39300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-70000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-42500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-9500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>145100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-40800</v>
       </c>
-      <c r="G102" s="3">
-        <v>79200</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-115600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>112900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-64300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>124700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>117900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>104400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-177200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>149800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-107800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-69200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-103000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-76400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-131900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-566500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>152400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-749500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>476400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>144200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-95500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>575000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>70500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>238900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-91200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>100600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-86200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>108500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-43400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>142300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>53800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>68900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-6900</v>
       </c>
     </row>
